--- a/data/trans_camb/P8_1_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P8_1_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 11,01</t>
+          <t>-1,18; 10,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 12,99</t>
+          <t>0,52; 12,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 8,77</t>
+          <t>-2,58; 8,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 17,36</t>
+          <t>3,54; 18,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 16,8</t>
+          <t>2,23; 16,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 6,93</t>
+          <t>-5,14; 6,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 12,12</t>
+          <t>2,66; 11,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 13,57</t>
+          <t>3,66; 13,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 6,37</t>
+          <t>-1,95; 6,26</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 117,23</t>
+          <t>-8,86; 113,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 140,62</t>
+          <t>4,26; 135,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 98,29</t>
+          <t>-17,97; 95,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,44; 116,68</t>
+          <t>16,02; 122,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 112,22</t>
+          <t>10,2; 114,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 47,35</t>
+          <t>-23,83; 49,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,92; 92,83</t>
+          <t>15,19; 95,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,57; 107,88</t>
+          <t>19,92; 106,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 51,64</t>
+          <t>-11,39; 49,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 6,97</t>
+          <t>-1,62; 7,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,86</t>
+          <t>-4,18; 4,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 8,61</t>
+          <t>-0,88; 8,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 8,83</t>
+          <t>-2,58; 8,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 2,52</t>
+          <t>-8,22; 2,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 4,11</t>
+          <t>-5,41; 4,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 6,71</t>
+          <t>-0,96; 6,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 1,52</t>
+          <t>-5,36; 1,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 5,33</t>
+          <t>-1,96; 5,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 66,3</t>
+          <t>-12,4; 71,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 40,22</t>
+          <t>-29,51; 40,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 86,53</t>
+          <t>-6,66; 78,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 40,46</t>
+          <t>-9,48; 40,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 11,94</t>
+          <t>-30,69; 10,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 18,72</t>
+          <t>-19,16; 20,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 40,77</t>
+          <t>-4,96; 39,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 9,51</t>
+          <t>-26,47; 10,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 33,14</t>
+          <t>-9,61; 30,96</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 12,35</t>
+          <t>2,14; 12,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 10,72</t>
+          <t>1,78; 10,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 10,33</t>
+          <t>1,52; 10,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 8,87</t>
+          <t>-3,9; 9,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 5,07</t>
+          <t>-7,48; 4,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 3,69</t>
+          <t>-8,08; 3,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 8,53</t>
+          <t>0,52; 8,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 6,09</t>
+          <t>-2,0; 5,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,3</t>
+          <t>-2,13; 5,16</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,61; 222,82</t>
+          <t>19,1; 223,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,82; 188,75</t>
+          <t>15,12; 209,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,22; 185,56</t>
+          <t>11,27; 199,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 48,34</t>
+          <t>-16,84; 49,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,98; 28,33</t>
+          <t>-30,91; 26,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 22,49</t>
+          <t>-32,19; 17,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 67,46</t>
+          <t>1,87; 69,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 47,03</t>
+          <t>-11,72; 47,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 42,68</t>
+          <t>-13,22; 41,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 10,73</t>
+          <t>0,42; 10,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 9,65</t>
+          <t>0,17; 10,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 15,61</t>
+          <t>4,56; 15,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 16,13</t>
+          <t>3,76; 16,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 11,62</t>
+          <t>-0,86; 11,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 4,35</t>
+          <t>-10,84; 4,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 12,01</t>
+          <t>3,82; 11,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 9,25</t>
+          <t>1,21; 9,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 7,67</t>
+          <t>-2,24; 7,95</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,51; 144,23</t>
+          <t>6,37; 143,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 125,75</t>
+          <t>2,45; 164,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,95; 211,46</t>
+          <t>37,37; 211,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,99; 90,6</t>
+          <t>15,95; 94,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 66,12</t>
+          <t>-3,1; 69,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,14; 21,97</t>
+          <t>-46,67; 25,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,22; 89,61</t>
+          <t>22,62; 90,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,72; 71,8</t>
+          <t>7,33; 72,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 58,18</t>
+          <t>-13,13; 58,55</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,89; 15,52</t>
+          <t>2,49; 15,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 10,75</t>
+          <t>0,12; 10,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 9,38</t>
+          <t>-0,02; 9,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,03; 19,63</t>
+          <t>3,25; 20,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 13,32</t>
+          <t>-1,75; 13,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 9,78</t>
+          <t>-7,82; 10,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 15,76</t>
+          <t>5,73; 15,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 10,07</t>
+          <t>0,39; 10,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 8,43</t>
+          <t>-1,87; 8,62</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>22,28; 302,36</t>
+          <t>22,98; 311,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 216,9</t>
+          <t>-0,55; 233,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 179,7</t>
+          <t>-2,87; 183,92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,59; 150,54</t>
+          <t>15,83; 163,12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 97,07</t>
+          <t>-9,18; 107,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-39,21; 72,15</t>
+          <t>-39,67; 72,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,39; 167,4</t>
+          <t>38,13; 154,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,46; 100,09</t>
+          <t>-0,67; 103,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 85,14</t>
+          <t>-9,31; 89,81</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,14; 13,58</t>
+          <t>1,39; 13,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,02; 16,36</t>
+          <t>3,85; 16,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 4,68</t>
+          <t>-4,65; 4,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 9,29</t>
+          <t>-4,8; 10,56</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 13,59</t>
+          <t>-1,36; 13,98</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -1,94</t>
+          <t>-14,16; -1,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,13; 9,8</t>
+          <t>-0,12; 9,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,78; 13,09</t>
+          <t>2,27; 12,51</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,72; -0,57</t>
+          <t>-8,63; -0,8</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7,39; 162,55</t>
+          <t>6,15; 163,29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27,68; 206,8</t>
+          <t>29,36; 201,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 58,22</t>
+          <t>-36,11; 58,8</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 44,23</t>
+          <t>-17,82; 50,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 64,63</t>
+          <t>-4,89; 65,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-49,15; -9,77</t>
+          <t>-48,49; -7,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,07; 63,67</t>
+          <t>-0,49; 59,94</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>13,21; 82,27</t>
+          <t>10,92; 80,76</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-41,65; -3,89</t>
+          <t>-41,7; -5,15</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 3,53</t>
+          <t>-3,64; 3,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,38</t>
+          <t>-2,95; 4,59</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 8,08</t>
+          <t>0,19; 8,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 6,64</t>
+          <t>-2,91; 6,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 4,59</t>
+          <t>-4,73; 4,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 3,91</t>
+          <t>-13,3; 3,78</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,31</t>
+          <t>-1,82; 4,21</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,7</t>
+          <t>-2,28; 3,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 3,94</t>
+          <t>-6,48; 4,4</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 34,59</t>
+          <t>-25,87; 33,07</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 54,55</t>
+          <t>-20,75; 44,26</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 76,66</t>
+          <t>1,57; 75,97</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 34,22</t>
+          <t>-12,08; 32,92</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 24,27</t>
+          <t>-19,4; 22,4</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-56,9; 19,32</t>
+          <t>-60,45; 18,66</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 28,05</t>
+          <t>-9,88; 26,84</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 23,98</t>
+          <t>-12,51; 25,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 23,41</t>
+          <t>-35,59; 26,99</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 4,79</t>
+          <t>-2,4; 4,57</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,87</t>
+          <t>-4,49; 1,97</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 57,54</t>
+          <t>-0,83; 58,04</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 4,57</t>
+          <t>-4,19; 4,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 3,0</t>
+          <t>-5,78; 2,68</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 7,5</t>
+          <t>-0,58; 7,73</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,38</t>
+          <t>-2,12; 3,47</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,32</t>
+          <t>-4,17; 1,26</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,1; 38,89</t>
+          <t>0,79; 39,4</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 41,44</t>
+          <t>-17,11; 38,98</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 16,88</t>
+          <t>-31,03; 16,61</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 526,04</t>
+          <t>-5,51; 521,08</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 24,55</t>
+          <t>-18,16; 23,22</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 15,9</t>
+          <t>-25,33; 14,49</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 39,98</t>
+          <t>-2,66; 41,64</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 21,62</t>
+          <t>-11,7; 22,2</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 8,35</t>
+          <t>-22,29; 8,27</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5,85; 225,42</t>
+          <t>4,44; 235,01</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,17</t>
+          <t>1,83; 5,22</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,21</t>
+          <t>1,14; 4,22</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,99; 27,54</t>
+          <t>3,12; 27,29</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,93</t>
+          <t>1,86; 5,83</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,13</t>
+          <t>-0,6; 3,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 1,23</t>
+          <t>-5,18; 1,21</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,09</t>
+          <t>2,5; 5,0</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,35</t>
+          <t>0,56; 3,27</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,66; 14,55</t>
+          <t>0,72; 13,34</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>15,04; 49,25</t>
+          <t>15,63; 50,04</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>8,69; 40,97</t>
+          <t>9,72; 40,77</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>25,68; 257,17</t>
+          <t>27,24; 254,99</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,08; 29,41</t>
+          <t>8,41; 28,86</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 15,36</t>
+          <t>-2,68; 16,41</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 5,78</t>
+          <t>-23,32; 5,83</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>13,25; 32,01</t>
+          <t>14,81; 31,62</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>3,56; 21,05</t>
+          <t>3,29; 20,84</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,72; 86,65</t>
+          <t>4,42; 82,99</t>
         </is>
       </c>
     </row>
